--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/observations-summary.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/observations-summary.xlsx
@@ -53,7 +53,7 @@
     <t>JP Core Observation BodyMeasurement Profile</t>
   </si>
   <si>
-    <t>JP Core Simple Observation Category CodeSystem#body-measurement</t>
+    <t>JP Core Simple Observation Category CodeSystem#body-measurement, JP Core Observation BodyMeasurement Category CodeSystem#null</t>
   </si>
   <si>
     <t/>
@@ -128,7 +128,7 @@
     <t>JP Core Observation Electrocardiogram Profile</t>
   </si>
   <si>
-    <t>JP Core Simple Observation Category CodeSystem#procedure, LOINC#11524-6</t>
+    <t>JP Core Simple Observation Category CodeSystem#procedure, LOINC#11524-6, JP Core Observation Electrocardiogram Extra Category CodeSystem#null</t>
   </si>
   <si>
     <t>LOINC#11524-6</t>
@@ -242,7 +242,7 @@
     <t>JP Core Observation VitalSigns Profile</t>
   </si>
   <si>
-    <t>JP Core Simple Observation Category CodeSystem#vital-signs</t>
+    <t>JP Core Simple Observation Category CodeSystem#vital-signs, JP Core Observation VitalSigns Category CodeSystem#null</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationVitalSignsCode_VS (preferred)</t>

--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/observations-summary.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/observations-summary.xlsx
@@ -197,7 +197,7 @@
     <t>null#physical-findings</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_PhysicalExamCode_VS (required)</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_PhysicalExamCode_VS (preferred)</t>
   </si>
   <si>
     <t>jp-observation-radiology-findings</t>
